--- a/stufe-5/labor/migration-test-ig-ptdata-1968/ValueSet-current-smoking-status-uv-ips.xlsx
+++ b/stufe-5/labor/migration-test-ig-ptdata-1968/ValueSet-current-smoking-status-uv-ips.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-10T12:42:05+00:00</t>
+    <t>2025-12-11T09:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
